--- a/AxisBank_BugReport.xlsx
+++ b/AxisBank_BugReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/13da4701092726d5/Testing/Axis Bank/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{55DE38B2-3BD8-4C01-AE3C-60A8259E2389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFDC84B7-710B-4525-97FD-60FA3220D718}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{55DE38B2-3BD8-4C01-AE3C-60A8259E2389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A882553-43C0-43C3-9587-8AAC89011B8B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Version History" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="199">
   <si>
     <t>BUG REPORT SUMMARY — AXIS BANK HOME PAGE</t>
   </si>
@@ -159,13 +159,7 @@
     <t>Creation Date</t>
   </si>
   <si>
-    <t>10-Jan-2025</t>
-  </si>
-  <si>
     <t>Approval Date</t>
-  </si>
-  <si>
-    <t>20-Feb-2025</t>
   </si>
   <si>
     <t>Bug ID</t>
@@ -983,51 +977,51 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1340,8 +1334,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" style="8" customWidth="1"/>
     <col min="7" max="7" width="7.5546875" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" customWidth="1"/>
     <col min="9" max="9" width="8.44140625" customWidth="1"/>
@@ -1430,9 +1424,7 @@
       <c r="A6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>45</v>
-      </c>
+      <c r="B6" s="18"/>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
@@ -1444,11 +1436,9 @@
     </row>
     <row r="7" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>47</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B7" s="18"/>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
       <c r="E7" s="19"/>
@@ -1487,7 +1477,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="24"/>
@@ -1509,11 +1499,11 @@
       <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="27">
+      <c r="B3" s="29"/>
+      <c r="C3" s="36">
         <v>18</v>
       </c>
       <c r="D3" s="24"/>
@@ -1523,11 +1513,11 @@
       <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="23" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="24"/>
-      <c r="C4" s="29">
+      <c r="C4" s="32">
         <v>3</v>
       </c>
       <c r="D4" s="24"/>
@@ -1537,11 +1527,11 @@
       <c r="H4" s="24"/>
     </row>
     <row r="5" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="23" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="24"/>
-      <c r="C5" s="29">
+      <c r="C5" s="32">
         <v>4</v>
       </c>
       <c r="D5" s="24"/>
@@ -1551,11 +1541,11 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="23" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="24"/>
-      <c r="C6" s="29">
+      <c r="C6" s="32">
         <v>11</v>
       </c>
       <c r="D6" s="24"/>
@@ -1565,11 +1555,11 @@
       <c r="H6" s="24"/>
     </row>
     <row r="7" spans="1:8" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="23" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="24"/>
-      <c r="C7" s="29">
+      <c r="C7" s="32">
         <v>18</v>
       </c>
       <c r="D7" s="24"/>
@@ -1589,37 +1579,37 @@
       <c r="H8" s="15"/>
     </row>
     <row r="9" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="34"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
     </row>
     <row r="10" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="31" t="s">
+      <c r="B10" s="35"/>
+      <c r="C10" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
     </row>
     <row r="11" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="31" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="24"/>
-      <c r="C11" s="36">
+      <c r="C11" s="25">
         <v>3</v>
       </c>
       <c r="D11" s="24"/>
@@ -1629,11 +1619,11 @@
       <c r="H11" s="24"/>
     </row>
     <row r="12" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="33" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="24"/>
-      <c r="C12" s="37">
+      <c r="C12" s="34">
         <v>4</v>
       </c>
       <c r="D12" s="24"/>
@@ -1643,11 +1633,11 @@
       <c r="H12" s="24"/>
     </row>
     <row r="13" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="31" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="24"/>
-      <c r="C13" s="36">
+      <c r="C13" s="25">
         <v>11</v>
       </c>
       <c r="D13" s="24"/>
@@ -1658,7 +1648,7 @@
     </row>
     <row r="14" spans="1:8" ht="24.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="39" t="s">
+      <c r="A15" s="30" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="24"/>
@@ -1670,11 +1660,11 @@
       <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
       <c r="D16" s="13" t="s">
         <v>14</v>
       </c>
@@ -1692,7 +1682,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="26" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="24"/>
@@ -1714,7 +1704,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="27" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="24"/>
@@ -1736,7 +1726,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="26" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="24"/>
@@ -1758,7 +1748,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="27" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="24"/>
@@ -1780,7 +1770,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="26" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="24"/>
@@ -1802,7 +1792,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="27" t="s">
         <v>25</v>
       </c>
       <c r="B22" s="24"/>
@@ -1824,7 +1814,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="26" t="s">
         <v>26</v>
       </c>
       <c r="B23" s="24"/>
@@ -1846,7 +1836,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="27" t="s">
         <v>27</v>
       </c>
       <c r="B24" s="24"/>
@@ -1868,7 +1858,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="26" t="s">
         <v>28</v>
       </c>
       <c r="B25" s="24"/>
@@ -1890,7 +1880,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="27" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="24"/>
@@ -1912,7 +1902,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="26" t="s">
         <v>30</v>
       </c>
       <c r="B27" s="24"/>
@@ -1934,7 +1924,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="27" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="24"/>
@@ -1956,7 +1946,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="32" t="s">
+      <c r="A29" s="26" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="24"/>
@@ -1978,7 +1968,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="26" t="s">
+      <c r="A30" s="27" t="s">
         <v>33</v>
       </c>
       <c r="B30" s="24"/>
@@ -2000,7 +1990,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="35" t="s">
         <v>34</v>
       </c>
       <c r="B31" s="24"/>
@@ -2021,27 +2011,6 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A30:C30"/>
@@ -2058,6 +2027,27 @@
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:H12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2083,66 +2073,66 @@
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>10</v>
@@ -2154,33 +2144,33 @@
         <v>20</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>70</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>10</v>
@@ -2192,109 +2182,109 @@
         <v>20</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>10</v>
@@ -2306,71 +2296,71 @@
         <v>20</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>100</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>11</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>9</v>
@@ -2382,109 +2372,109 @@
         <v>20</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="H9" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="H11" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>132</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>9</v>
@@ -2496,147 +2486,147 @@
         <v>20</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>150</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>11</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>20</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>163</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>167</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>9</v>
@@ -2648,147 +2638,147 @@
         <v>20</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="H16" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>20</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>179</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>181</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>183</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>11</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>20</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="94.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>195</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>33</v>
       </c>
       <c r="E19" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>197</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>199</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>10</v>
@@ -2800,7 +2790,7 @@
         <v>20</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
